--- a/artfynd/S 491-2025 artfynd.xlsx
+++ b/artfynd/S 491-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -811,6 +816,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122125947</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -950,6 +960,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122125949</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1089,6 +1104,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122125950</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1228,6 +1248,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126954</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1367,6 +1392,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126957</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1506,6 +1536,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126959</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1645,6 +1680,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126960</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1784,6 +1824,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126961</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1923,6 +1968,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126962</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2062,6 +2112,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126968</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2201,6 +2256,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126969</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2340,6 +2400,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126971</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2479,6 +2544,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126974</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2618,6 +2688,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126975</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2757,6 +2832,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126982</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2896,6 +2976,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126983</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3035,6 +3120,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126985</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3174,6 +3264,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126270</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3313,6 +3408,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126272</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3452,6 +3552,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126273</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3591,6 +3696,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126287</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3730,6 +3840,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126288</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3869,6 +3984,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126289</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4008,6 +4128,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126290</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4147,6 +4272,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126293</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4286,6 +4416,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126294</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4425,6 +4560,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126295</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4564,6 +4704,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126296</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4703,6 +4848,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126298</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4842,6 +4992,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126299</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4981,6 +5136,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126301</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5120,6 +5280,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126304</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5259,6 +5424,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126305</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5398,6 +5568,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126306</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5537,6 +5712,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126050</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5676,6 +5856,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126059</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5815,6 +6000,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126060</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5954,6 +6144,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126061</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6093,6 +6288,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126062</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6232,6 +6432,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126063</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6371,6 +6576,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126064</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6510,6 +6720,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126066</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6649,6 +6864,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126067</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6788,6 +7008,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126068</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6927,6 +7152,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126069</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7066,6 +7296,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126071</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7205,6 +7440,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126075</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7344,6 +7584,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126076</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7483,6 +7728,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126077</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7622,6 +7872,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126081</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7761,6 +8016,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126082</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7900,6 +8160,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126083</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8039,6 +8304,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126142</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8178,6 +8448,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126143</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8317,6 +8592,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126144</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8456,6 +8736,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126145</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8595,6 +8880,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126146</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8734,6 +9024,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126147</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8873,6 +9168,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126148</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -9012,6 +9312,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126151</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9151,6 +9456,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126152</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9290,6 +9600,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126153</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9429,6 +9744,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126154</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9568,6 +9888,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126156</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9707,8 +10032,80 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126157</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>